--- a/public/apprenants-model.xlsx
+++ b/public/apprenants-model.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
   <si>
     <t>Nom</t>
   </si>
@@ -32,9 +32,6 @@
     <t>Prénom</t>
   </si>
   <si>
-    <t>GOGO</t>
-  </si>
-  <si>
     <t>Apprenant 1</t>
   </si>
   <si>
@@ -50,31 +47,25 @@
     <t>A</t>
   </si>
   <si>
-    <t>Parent(nom - Prénom)</t>
-  </si>
-  <si>
-    <t>GOGO-Parent 4</t>
-  </si>
-  <si>
     <t>Sexe</t>
   </si>
   <si>
     <t>Masculin</t>
   </si>
   <si>
-    <t>GOGO-Parent 2</t>
-  </si>
-  <si>
     <t>Apprenant 2</t>
   </si>
   <si>
-    <t>IMMA</t>
-  </si>
-  <si>
     <t>Féminin</t>
   </si>
   <si>
     <t>B</t>
+  </si>
+  <si>
+    <t>MAMRE</t>
+  </si>
+  <si>
+    <t>Parent(phone)</t>
   </si>
 </sst>
 </file>
@@ -133,10 +124,10 @@
   </cellStyles>
   <dxfs count="8">
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -175,10 +166,10 @@
   <tableColumns count="6">
     <tableColumn id="1" name="Nom" dataDxfId="5"/>
     <tableColumn id="2" name="Prénom" dataDxfId="4"/>
-    <tableColumn id="5" name="Parent(nom - Prénom)" dataDxfId="3"/>
+    <tableColumn id="5" name="Parent(phone)" dataDxfId="3"/>
     <tableColumn id="6" name="Serie" dataDxfId="2"/>
-    <tableColumn id="3" name="Sexe" dataDxfId="0"/>
-    <tableColumn id="4" name="Classe" dataDxfId="1"/>
+    <tableColumn id="3" name="Sexe" dataDxfId="1"/>
+    <tableColumn id="4" name="Classe" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -466,56 +457,56 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>9</v>
+      <c r="C2" s="3">
+        <v>2233</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>12</v>
+        <v>9</v>
+      </c>
+      <c r="C3" s="3">
+        <v>2295681</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
